--- a/Team-Data/2014-15/2-23-2014-15.xlsx
+++ b/Team-Data/2014-15/2-23-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -775,10 +842,10 @@
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>30</v>
@@ -799,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -808,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.389</v>
+        <v>0.377</v>
       </c>
       <c r="H3" t="n">
         <v>48.6</v>
       </c>
       <c r="I3" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J3" t="n">
         <v>88.09999999999999</v>
@@ -867,25 +934,25 @@
         <v>0.444</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M3" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.328</v>
+        <v>0.324</v>
       </c>
       <c r="O3" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P3" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S3" t="n">
         <v>32.7</v>
@@ -900,28 +967,28 @@
         <v>14.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X3" t="n">
         <v>3.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -942,16 +1009,16 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM3" t="n">
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -966,13 +1033,13 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -984,16 +1051,16 @@
         <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.426</v>
+        <v>0.415</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J4" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>6.6</v>
@@ -1055,7 +1122,7 @@
         <v>20.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.321</v>
+        <v>0.324</v>
       </c>
       <c r="O4" t="n">
         <v>16.4</v>
@@ -1064,28 +1131,28 @@
         <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S4" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>41.9</v>
       </c>
       <c r="U4" t="n">
         <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
         <v>4.5</v>
@@ -1097,16 +1164,16 @@
         <v>19.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>17</v>
@@ -1136,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
         <v>19</v>
@@ -1151,13 +1218,13 @@
         <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1166,19 +1233,19 @@
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -1285,10 +1352,10 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
@@ -1330,10 +1397,10 @@
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>0.632</v>
+        <v>0.625</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L6" t="n">
         <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0.787</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="T6" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="U6" t="n">
         <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W6" t="n">
         <v>6.3</v>
@@ -1461,16 +1528,16 @@
         <v>21.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.9</v>
+        <v>102.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
@@ -1482,22 +1549,22 @@
         <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,13 +1576,13 @@
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>14</v>
@@ -1539,7 +1606,7 @@
         <v>3</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>3.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1670,7 +1737,7 @@
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1679,13 +1746,13 @@
         <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
@@ -1694,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
         <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.655</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J8" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
         <v>0.463</v>
@@ -1780,10 +1847,10 @@
         <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O8" t="n">
         <v>16.6</v>
@@ -1792,28 +1859,28 @@
         <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V8" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
@@ -1825,10 +1892,10 @@
         <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,13 +1904,13 @@
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1852,7 +1919,7 @@
         <v>6</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>6</v>
@@ -1861,19 +1928,19 @@
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>18</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
-        <v>86.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.429</v>
+        <v>0.431</v>
       </c>
       <c r="L9" t="n">
         <v>7.4</v>
       </c>
       <c r="M9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="O9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P9" t="n">
         <v>24.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R9" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S9" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T9" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U9" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V9" t="n">
         <v>14.1</v>
@@ -1998,7 +2065,7 @@
         <v>4.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z9" t="n">
         <v>23</v>
@@ -2007,25 +2074,25 @@
         <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.3</v>
+        <v>-3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF9" t="n">
         <v>24</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>18</v>
@@ -2043,49 +2110,49 @@
         <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>23</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -2195,10 +2262,10 @@
         <v>-1</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF10" t="n">
         <v>20</v>
@@ -2228,7 +2295,7 @@
         <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2258,7 +2325,7 @@
         <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
@@ -2267,7 +2334,7 @@
         <v>21</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2416,7 +2483,7 @@
         <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2437,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -2496,40 +2563,40 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.717</v>
+        <v>0.716</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
         <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>21.7</v>
@@ -2538,7 +2605,7 @@
         <v>17.1</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.7</v>
@@ -2547,19 +2614,19 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2574,10 +2641,10 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>13</v>
@@ -2616,10 +2683,10 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
         <v>24</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>-1</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF13" t="n">
         <v>20</v>
@@ -2753,16 +2820,16 @@
         <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
@@ -2774,7 +2841,7 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
@@ -2783,7 +2850,7 @@
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
         <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.649</v>
+        <v>0.661</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2875,13 +2942,13 @@
         <v>26.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O14" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P14" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q14" t="n">
         <v>0.73</v>
@@ -2890,49 +2957,49 @@
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W14" t="n">
         <v>7.9</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y14" t="n">
         <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>107.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -2983,7 +3050,7 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.259</v>
+        <v>0.255</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
         <v>0.346</v>
       </c>
       <c r="O15" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R15" t="n">
         <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y15" t="n">
         <v>4.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>24</v>
@@ -3135,16 +3202,16 @@
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
@@ -3153,10 +3220,10 @@
         <v>17</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>6</v>
@@ -3168,16 +3235,16 @@
         <v>19</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB15" t="n">
         <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="H16" t="n">
         <v>48.8</v>
       </c>
       <c r="I16" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J16" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L16" t="n">
         <v>5.3</v>
@@ -3245,25 +3312,25 @@
         <v>18.4</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
         <v>32.6</v>
       </c>
       <c r="T16" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U16" t="n">
         <v>22</v>
       </c>
       <c r="V16" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W16" t="n">
         <v>8.5</v>
@@ -3272,22 +3339,22 @@
         <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.3</v>
+        <v>100.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3329,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>12</v>
@@ -3353,7 +3420,7 @@
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>12</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>75.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.457</v>
+        <v>0.455</v>
       </c>
       <c r="L17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O17" t="n">
         <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R17" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T17" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="U17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V17" t="n">
         <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
         <v>4.2</v>
@@ -3463,13 +3530,13 @@
         <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,16 +3557,16 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3508,7 +3575,7 @@
         <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV17" t="n">
         <v>20</v>
@@ -3535,7 +3602,7 @@
         <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
@@ -3544,7 +3611,7 @@
         <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
         <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.554</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J18" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.462</v>
+        <v>0.465</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
         <v>18.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.373</v>
+        <v>0.376</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="R18" t="n">
         <v>10</v>
@@ -3624,10 +3691,10 @@
         <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V18" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="W18" t="n">
         <v>9.5</v>
@@ -3636,7 +3703,7 @@
         <v>4.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z18" t="n">
         <v>22.3</v>
@@ -3645,13 +3712,13 @@
         <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,7 +3730,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
@@ -3672,10 +3739,10 @@
         <v>25</v>
       </c>
       <c r="AK18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>25</v>
@@ -3684,19 +3751,19 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR18" t="n">
         <v>25</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
         <v>26</v>
@@ -3711,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
@@ -3720,10 +3787,10 @@
         <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
         <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>0.218</v>
+        <v>0.222</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J19" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O19" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.761</v>
+        <v>0.757</v>
       </c>
       <c r="R19" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="T19" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>8.4</v>
@@ -3821,19 +3888,19 @@
         <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC19" t="n">
         <v>-8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3848,13 +3915,13 @@
         <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="n">
         <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3869,13 +3936,13 @@
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3896,10 +3963,10 @@
         <v>26</v>
       </c>
       <c r="AY19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -3955,67 +4022,67 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>83.2</v>
+        <v>83.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L20" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>16</v>
@@ -4024,19 +4091,19 @@
         <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>23</v>
@@ -4045,40 +4112,40 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT20" t="n">
         <v>10</v>
       </c>
-      <c r="AR20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>15</v>
-      </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>18</v>
@@ -4227,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4239,7 +4306,7 @@
         <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4251,13 +4318,13 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4446,22 @@
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4409,10 +4476,10 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
@@ -4421,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4433,7 +4500,7 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4442,16 +4509,16 @@
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O23" t="n">
         <v>14.2</v>
@@ -4522,31 +4589,31 @@
         <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
@@ -4555,10 +4622,10 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.5</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4576,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4591,7 +4658,7 @@
         <v>23</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>20</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>0.214</v>
+        <v>0.218</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="J24" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.412</v>
+        <v>0.411</v>
       </c>
       <c r="L24" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M24" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.314</v>
+        <v>0.312</v>
       </c>
       <c r="O24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.681</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R24" t="n">
         <v>11.4</v>
       </c>
       <c r="S24" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U24" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="W24" t="n">
         <v>9.800000000000001</v>
@@ -4731,19 +4798,19 @@
         <v>5.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA24" t="n">
         <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4773,13 +4840,13 @@
         <v>11</v>
       </c>
       <c r="AN24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4791,7 +4858,7 @@
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>27</v>
@@ -4800,19 +4867,19 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
         <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.509</v>
+        <v>0.518</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J25" t="n">
-        <v>86.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.462</v>
@@ -4874,16 +4941,16 @@
         <v>9.5</v>
       </c>
       <c r="M25" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O25" t="n">
         <v>16.6</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0.78</v>
@@ -4892,10 +4959,10 @@
         <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U25" t="n">
         <v>20.8</v>
@@ -4910,34 +4977,34 @@
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z25" t="n">
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -4955,10 +5022,10 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -4967,19 +5034,19 @@
         <v>4</v>
       </c>
       <c r="AR25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>4.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
         <v>9</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5149,13 +5216,13 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -5164,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
@@ -5179,7 +5246,7 @@
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,7 +5398,7 @@
         <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
         <v>5</v>
@@ -5352,16 +5419,16 @@
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -5396,55 +5463,55 @@
         <v>55</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6</v>
+        <v>0.618</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="O28" t="n">
         <v>16.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
         <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="V28" t="n">
         <v>14.3</v>
@@ -5453,7 +5520,7 @@
         <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5462,37 +5529,37 @@
         <v>19.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.5</v>
+        <v>100.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
       </c>
       <c r="AF28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG28" t="n">
         <v>10</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK28" t="n">
         <v>11</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>12</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,31 +5568,31 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>20</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5540,7 +5607,7 @@
         <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>13</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -5575,22 +5642,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
         <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>0.661</v>
+        <v>0.673</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J29" t="n">
         <v>84.09999999999999</v>
@@ -5599,40 +5666,40 @@
         <v>0.454</v>
       </c>
       <c r="L29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M29" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="O29" t="n">
         <v>19.8</v>
       </c>
       <c r="P29" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="R29" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
         <v>42</v>
       </c>
       <c r="U29" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X29" t="n">
         <v>4.6</v>
@@ -5641,40 +5708,40 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AA29" t="n">
         <v>21.2</v>
       </c>
-      <c r="AA29" t="n">
-        <v>21.1</v>
-      </c>
       <c r="AB29" t="n">
-        <v>104.9</v>
+        <v>105.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>8</v>
       </c>
       <c r="AJ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK29" t="n">
         <v>13</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5683,31 +5750,31 @@
         <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW29" t="n">
         <v>13</v>
@@ -5728,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
         <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.382</v>
+        <v>0.37</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,19 +5842,19 @@
         <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
         <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
         <v>16.6</v>
@@ -5796,25 +5863,25 @@
         <v>22.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R30" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T30" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U30" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X30" t="n">
         <v>5.9</v>
@@ -5823,19 +5890,19 @@
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA30" t="n">
         <v>19.1</v>
       </c>
-      <c r="AA30" t="n">
-        <v>19.2</v>
-      </c>
       <c r="AB30" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5868,7 +5935,7 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5880,28 +5947,28 @@
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW30" t="n">
         <v>23</v>
       </c>
-      <c r="AW30" t="n">
-        <v>22</v>
-      </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
         <v>25</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>1.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6050,16 +6117,16 @@
         <v>5</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR31" t="n">
         <v>20</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>19</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
@@ -6068,25 +6135,25 @@
         <v>9</v>
       </c>
       <c r="AU31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-23-2014-15</t>
+          <t>2015-02-23</t>
         </is>
       </c>
     </row>
